--- a/Document/DAB1/DAB.xlsx
+++ b/Document/DAB1/DAB.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\DAB1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AF1AC8-7012-4055-B134-0A1F49D706AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5827B8-A0BE-4FB7-9112-1FC230DADF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="12585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="matlab reference" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,22 +26,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>sps control</t>
   </si>
   <si>
     <t>EPS control</t>
   </si>
+  <si>
+    <t>https://ww2.mathworks.cn/matlabcentral/fileexchange/182900-dual-active-bridge-dc-dc-converter-with-phase-shift-control?s_tid=FX_rc3_behav</t>
+  </si>
+  <si>
+    <t>(10 条消息) DAB变换器SPS环路设计—基于Simulink扫频Bode图法 - 知乎</t>
+  </si>
+  <si>
+    <t>DAB变换器EPS调制仿真：四种控制策略对比与Simulink实现-CSDN博客</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -63,13 +81,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -544,4 +565,33 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E774FC3-004C-45F8-A1B1-55EC4E628B76}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" display="https://zhuanlan.zhihu.com/p/354933447" xr:uid="{480D9CAE-F342-4271-B9F0-E6F2C70D51B1}"/>
+    <hyperlink ref="A5" r:id="rId2" display="https://blog.csdn.net/weixin_29278805/article/details/166569330" xr:uid="{1C9265C9-109C-4D31-9E49-7F38212FAF67}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>